--- a/Grupo/ULA_Grupo.xlsx
+++ b/Grupo/ULA_Grupo.xlsx
@@ -458,16 +458,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>51.42835335358198</v>
+        <v>51.428353353582</v>
       </c>
       <c r="C2" s="2">
-        <v>117.0063329534167</v>
+        <v>116.9943453466894</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>60.17443035735176</v>
+        <v>60.16826532860548</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>3.840631961716056</v>
+        <v>3.840631961716055</v>
       </c>
       <c r="C6" s="2">
         <v>110.3296953370247</v>
@@ -611,10 +611,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>4.254204955815808</v>
+        <v>4.254204955815807</v>
       </c>
       <c r="C11" s="2">
-        <v>125.2704440630567</v>
+        <v>125.2704440630568</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>6</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="2">
-        <v>1.729415562936943</v>
+        <v>1.729415562936944</v>
       </c>
     </row>
   </sheetData>
